--- a/examples/hide-rows.xlsx
+++ b/examples/hide-rows.xlsx
@@ -6,7 +6,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Hidden rows" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Hidden rows"/>
   </sheets>
   <definedNames/>
   <calcPr/>
